--- a/artfynd/A 53298-2022 artfynd.xlsx
+++ b/artfynd/A 53298-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53298-2022 artfynd.xlsx
+++ b/artfynd/A 53298-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80283006</v>
+        <v>97758162</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
+          <t>Sveds tallskog, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447313.4093573572</v>
+        <v>447199</v>
       </c>
       <c r="R2" t="n">
-        <v>6430374.925783207</v>
+        <v>6430438</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,27 +735,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Gustav Adolf</t>
+          <t>Habo</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-10-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,24 +754,355 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>79773302</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>447382</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6430307</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-09-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-09-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Niklas Johansson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Niklas Johansson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>80283006</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>447313</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6430375</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-10-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-10-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89140762</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väster om Axtorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>447438</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6430373</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 53298-2022 artfynd.xlsx
+++ b/artfynd/A 53298-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97758162</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79773302</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80283006</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,8 +1125,19 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89140762</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>